--- a/03_Prompting/outputs/GPT/RESULT_pan_gpt-4o_persona_fewshot_cot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_pan_gpt-4o_persona_fewshot_cot.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12682,7 +12682,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16626,7 +16626,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -18275,7 +18275,7 @@
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -20536,7 +20536,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21097,7 +21097,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -21335,7 +21335,7 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21352,7 +21352,7 @@
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21539,7 +21539,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -22525,7 +22525,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -22593,7 +22593,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22627,7 +22627,7 @@
       </c>
       <c r="C1306" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="C1361" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23596,7 +23596,7 @@
       </c>
       <c r="C1363" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8057553956834532</v>
+        <v>0.7985611510791367</v>
       </c>
     </row>
     <row r="3">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7451473468660968</v>
+        <v>0.714403228824691</v>
       </c>
     </row>
     <row r="4">
@@ -24129,7 +24129,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8030148714361844</v>
+        <v>0.7909796525151011</v>
       </c>
     </row>
     <row r="5">
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8053944978897639</v>
+        <v>0.8121590354455696</v>
       </c>
     </row>
     <row r="6">
@@ -24149,7 +24149,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7308675037327061</v>
+        <v>0.7008751608966565</v>
       </c>
     </row>
     <row r="7">
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>272.844557022001</v>
+        <v>751.6178407729894</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1962910482172669</v>
+        <v>0.5407322595489132</v>
       </c>
     </row>
   </sheetData>
